--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T09:56:07+00:00</t>
+    <t>2026-02-16T16:30:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T16:30:02+00:00</t>
+    <t>2026-02-16T17:09:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T17:09:53+00:00</t>
+    <t>2026-02-17T08:04:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:04:39+00:00</t>
+    <t>2026-02-17T08:46:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T08:46:02+00:00</t>
+    <t>2026-02-17T09:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:04:14+00:00</t>
+    <t>2026-02-17T09:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:45+00:00</t>
+    <t>2026-02-17T10:22:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:22:56+00:00</t>
+    <t>2026-04-14T15:08:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:08:12+00:00</t>
+    <t>2026-04-14T15:34:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5679" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="927">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:34:16+00:00</t>
+    <t>2026-04-30T09:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,11 @@
     <t>Full representation of the dosage instructions</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -4328,7 +4332,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -4386,7 +4392,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -4398,7 +4404,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -4409,13 +4415,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>81</v>
@@ -4437,13 +4443,13 @@
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4503,7 +4509,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -4526,10 +4532,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4552,13 +4558,13 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -4609,7 +4615,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -4630,7 +4636,7 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -4641,10 +4647,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4715,7 +4721,7 @@
         <v>138</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>81</v>
@@ -4724,7 +4730,7 @@
         <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4756,10 +4762,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4785,13 +4791,13 @@
         <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4799,7 +4805,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>81</v>
@@ -4841,7 +4847,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -4873,17 +4879,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>79</v>
@@ -4901,13 +4907,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4934,13 +4940,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4958,7 +4964,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4990,10 +4996,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -5016,13 +5022,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -5073,7 +5079,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -5094,7 +5100,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -5105,14 +5111,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -5134,13 +5140,13 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -5181,7 +5187,7 @@
         <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
@@ -5190,7 +5196,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -5211,7 +5217,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -5222,10 +5228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5248,19 +5254,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -5309,7 +5315,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -5330,21 +5336,21 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5367,19 +5373,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -5428,7 +5434,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -5449,25 +5455,25 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5489,16 +5495,16 @@
         <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -5547,7 +5553,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -5579,10 +5585,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5605,16 +5611,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5664,7 +5670,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -5679,27 +5685,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5725,13 +5731,13 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5757,13 +5763,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -5781,7 +5787,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -5796,16 +5802,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5813,10 +5819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5839,16 +5845,16 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5874,13 +5880,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5898,7 +5904,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5913,13 +5919,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -5930,10 +5936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5959,13 +5965,13 @@
         <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5991,13 +5997,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -6015,7 +6021,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -6030,16 +6036,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -6047,10 +6053,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6073,16 +6079,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -6108,13 +6114,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -6132,7 +6138,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -6150,13 +6156,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -6164,10 +6170,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6193,10 +6199,10 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6223,13 +6229,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -6247,7 +6253,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -6262,16 +6268,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -6279,10 +6285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6305,16 +6311,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6364,7 +6370,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -6385,7 +6391,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -6396,10 +6402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6422,13 +6428,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6479,7 +6485,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -6500,7 +6506,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -6511,10 +6517,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6537,16 +6543,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6572,29 +6578,29 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -6609,30 +6615,30 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>81</v>
@@ -6654,16 +6660,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6713,7 +6719,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>90</v>
@@ -6728,30 +6734,30 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
@@ -6773,16 +6779,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6808,11 +6814,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -6830,7 +6836,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>90</v>
@@ -6845,27 +6851,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6888,16 +6894,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6947,7 +6953,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6962,27 +6968,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7005,16 +7011,16 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -7064,7 +7070,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -7079,27 +7085,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7122,13 +7128,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7179,7 +7185,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -7194,16 +7200,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -7211,10 +7217,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7237,13 +7243,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7294,7 +7300,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -7315,7 +7321,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -7326,14 +7332,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7355,13 +7361,13 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7402,7 +7408,7 @@
         <v>138</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
@@ -7411,7 +7417,7 @@
         <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -7432,7 +7438,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -7443,13 +7449,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="B37" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="C37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>81</v>
@@ -7471,13 +7477,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7528,7 +7534,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7560,10 +7566,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7586,16 +7592,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7645,7 +7651,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7654,7 +7660,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -7677,10 +7683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7706,13 +7712,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7738,13 +7744,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -7762,7 +7768,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7794,10 +7800,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7820,16 +7826,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7879,7 +7885,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7900,7 +7906,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -7911,10 +7917,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7937,16 +7943,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7996,7 +8002,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -8028,10 +8034,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8054,13 +8060,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8111,7 +8117,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -8126,27 +8132,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8169,13 +8175,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8226,7 +8232,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -8241,16 +8247,16 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -8258,10 +8264,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8284,13 +8290,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8341,7 +8347,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8356,16 +8362,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -8373,10 +8379,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8399,16 +8405,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8434,13 +8440,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -8458,7 +8464,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8473,13 +8479,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -8490,10 +8496,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8516,13 +8522,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8573,7 +8579,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8594,10 +8600,10 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -8605,10 +8611,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8631,16 +8637,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8666,13 +8672,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -8690,7 +8696,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8705,27 +8711,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8748,16 +8754,16 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8807,7 +8813,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8822,16 +8828,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -8839,10 +8845,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8865,13 +8871,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8922,7 +8928,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8937,13 +8943,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -8954,10 +8960,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8983,10 +8989,10 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9037,7 +9043,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -9058,7 +9064,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -9069,10 +9075,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9095,13 +9101,13 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9152,7 +9158,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -9167,13 +9173,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -9184,10 +9190,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9210,17 +9216,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -9269,7 +9275,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9284,13 +9290,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -9301,10 +9307,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9327,16 +9333,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9362,13 +9368,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -9386,7 +9392,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -9407,7 +9413,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -9418,10 +9424,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9444,13 +9450,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9501,7 +9507,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -9516,13 +9522,13 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -9533,10 +9539,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9559,13 +9565,13 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9616,7 +9622,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9631,13 +9637,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -9648,10 +9654,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9674,13 +9680,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9731,7 +9737,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9752,7 +9758,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -9763,14 +9769,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9792,13 +9798,13 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9839,7 +9845,7 @@
         <v>138</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>81</v>
@@ -9848,7 +9854,7 @@
         <v>139</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9869,7 +9875,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -9880,13 +9886,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="B58" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="C58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>81</v>
@@ -9908,16 +9914,16 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9967,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9999,10 +10005,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10025,16 +10031,16 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10084,7 +10090,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -10105,7 +10111,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -10116,10 +10122,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10142,13 +10148,13 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10199,7 +10205,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -10220,7 +10226,7 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -10231,10 +10237,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10257,13 +10263,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10314,7 +10320,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>90</v>
@@ -10335,7 +10341,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -10346,10 +10352,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10372,16 +10378,16 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10431,7 +10437,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10446,13 +10452,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -10463,10 +10469,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10489,13 +10495,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10546,7 +10552,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10567,7 +10573,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -10578,14 +10584,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10607,13 +10613,13 @@
         <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10654,7 +10660,7 @@
         <v>138</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
@@ -10663,7 +10669,7 @@
         <v>139</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10684,7 +10690,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -10695,14 +10701,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10724,16 +10730,16 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10782,7 +10788,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10814,10 +10820,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10840,17 +10846,17 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10899,7 +10905,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10920,21 +10926,21 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10957,17 +10963,17 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -11016,7 +11022,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11037,21 +11043,21 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11074,19 +11080,19 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -11111,13 +11117,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -11135,7 +11141,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11156,21 +11162,21 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11193,13 +11199,13 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11250,7 +11256,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11271,21 +11277,21 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11308,19 +11314,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11369,7 +11375,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11390,7 +11396,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -11401,10 +11407,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11427,13 +11433,13 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11484,7 +11490,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11505,7 +11511,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -11516,14 +11522,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11545,13 +11551,13 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11592,7 +11598,7 @@
         <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>81</v>
@@ -11601,7 +11607,7 @@
         <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11622,7 +11628,7 @@
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -11633,14 +11639,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11662,16 +11668,16 @@
         <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11720,7 +11726,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11752,10 +11758,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11778,17 +11784,17 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11837,7 +11843,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11858,7 +11864,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11869,10 +11875,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11895,17 +11901,17 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11954,7 +11960,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11966,7 +11972,7 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -11975,7 +11981,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -11986,10 +11992,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12012,13 +12018,13 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12069,7 +12075,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -12090,7 +12096,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -12101,14 +12107,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12130,13 +12136,13 @@
         <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12177,7 +12183,7 @@
         <v>138</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>81</v>
@@ -12186,7 +12192,7 @@
         <v>139</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -12207,7 +12213,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -12218,13 +12224,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="B78" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="C78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>81</v>
@@ -12246,13 +12252,13 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12303,7 +12309,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12335,10 +12341,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12361,13 +12367,13 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12418,7 +12424,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12439,7 +12445,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -12450,10 +12456,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12476,19 +12482,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -12537,7 +12543,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12558,7 +12564,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -12569,10 +12575,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12595,13 +12601,13 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12652,7 +12658,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12673,7 +12679,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -12684,10 +12690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12710,19 +12716,19 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12771,7 +12777,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12792,7 +12798,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12803,10 +12809,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12829,19 +12835,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12890,7 +12896,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12911,7 +12917,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -12922,10 +12928,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12951,10 +12957,10 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12981,13 +12987,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -13005,7 +13011,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -13026,7 +13032,7 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -13037,10 +13043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13063,13 +13069,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13077,7 +13083,7 @@
         <v>81</v>
       </c>
       <c r="Q85" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="R85" t="s" s="2">
         <v>81</v>
@@ -13122,7 +13128,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -13143,7 +13149,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -13154,10 +13160,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13180,13 +13186,13 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13237,7 +13243,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -13258,7 +13264,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -13269,10 +13275,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13295,13 +13301,13 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13352,7 +13358,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13373,7 +13379,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -13384,10 +13390,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13410,13 +13416,13 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13467,7 +13473,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13488,7 +13494,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -13499,10 +13505,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13528,10 +13534,10 @@
         <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13558,13 +13564,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13582,7 +13588,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13603,7 +13609,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -13614,10 +13620,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13643,13 +13649,13 @@
         <v>110</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13675,11 +13681,11 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13697,7 +13703,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13718,7 +13724,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13729,10 +13735,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13755,16 +13761,16 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13814,7 +13820,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13835,7 +13841,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13846,10 +13852,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13875,16 +13881,16 @@
         <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -13909,13 +13915,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13933,7 +13939,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13954,7 +13960,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13965,10 +13971,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13991,13 +13997,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14048,7 +14054,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14069,7 +14075,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -14080,10 +14086,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14106,16 +14112,16 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14144,10 +14150,10 @@
         <v>114</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -14165,7 +14171,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14186,7 +14192,7 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
@@ -14197,10 +14203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14223,16 +14229,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14258,13 +14264,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -14282,7 +14288,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14303,21 +14309,21 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14340,19 +14346,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14377,13 +14383,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -14401,7 +14407,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14422,21 +14428,21 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14459,17 +14465,17 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -14494,11 +14500,11 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14516,7 +14522,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14537,21 +14543,21 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14574,19 +14580,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14611,11 +14617,11 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -14633,7 +14639,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14654,21 +14660,21 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14691,13 +14697,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14748,7 +14754,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14775,15 +14781,15 @@
         <v>81</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14806,13 +14812,13 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14863,7 +14869,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14884,7 +14890,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14895,14 +14901,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14924,13 +14930,13 @@
         <v>135</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14971,7 +14977,7 @@
         <v>138</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
@@ -14980,7 +14986,7 @@
         <v>139</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -15001,7 +15007,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -15012,13 +15018,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="B102" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="C102" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>81</v>
@@ -15040,13 +15046,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15097,7 +15103,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -15129,10 +15135,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15155,17 +15161,17 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -15190,13 +15196,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -15214,7 +15220,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15241,15 +15247,15 @@
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15272,19 +15278,19 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15321,17 +15327,17 @@
         <v>81</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15352,24 +15358,24 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>81</v>
@@ -15391,19 +15397,19 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -15452,7 +15458,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15473,24 +15479,24 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>81</v>
@@ -15512,19 +15518,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15573,7 +15579,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15594,21 +15600,21 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15631,19 +15637,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -15680,17 +15686,17 @@
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15711,24 +15717,24 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
@@ -15750,19 +15756,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15811,7 +15817,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15832,24 +15838,24 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>81</v>
@@ -15871,19 +15877,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15932,7 +15938,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15953,24 +15959,24 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -15992,19 +15998,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -16053,7 +16059,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16074,21 +16080,21 @@
         <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16111,19 +16117,19 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -16172,7 +16178,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -16193,21 +16199,21 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16230,13 +16236,13 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16287,7 +16293,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16308,7 +16314,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -16319,14 +16325,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16348,13 +16354,13 @@
         <v>135</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16395,7 +16401,7 @@
         <v>138</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>81</v>
@@ -16404,7 +16410,7 @@
         <v>139</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16425,7 +16431,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -16436,10 +16442,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16462,13 +16468,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16519,7 +16525,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16540,7 +16546,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -16551,10 +16557,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16577,13 +16583,13 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16634,7 +16640,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16655,7 +16661,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16666,10 +16672,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16692,19 +16698,19 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16753,7 +16759,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16774,7 +16780,7 @@
         <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
@@ -16785,10 +16791,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16811,17 +16817,17 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16870,7 +16876,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16891,7 +16897,7 @@
         <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
@@ -16902,10 +16908,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16928,13 +16934,13 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16985,7 +16991,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -17003,10 +17009,10 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -17017,10 +17023,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17043,13 +17049,13 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17100,7 +17106,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -17121,7 +17127,7 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -17132,14 +17138,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17161,13 +17167,13 @@
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17217,7 +17223,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17238,7 +17244,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -17249,14 +17255,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17278,16 +17284,16 @@
         <v>135</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -17336,7 +17342,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17368,10 +17374,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17394,16 +17400,16 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17453,7 +17459,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17474,7 +17480,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -17485,10 +17491,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17511,13 +17517,13 @@
         <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17568,7 +17574,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17589,7 +17595,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17600,14 +17606,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -17629,13 +17635,13 @@
         <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17685,7 +17691,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17706,7 +17712,7 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
@@ -17717,14 +17723,14 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17746,16 +17752,16 @@
         <v>135</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17804,7 +17810,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17836,10 +17842,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17862,13 +17868,13 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17919,7 +17925,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17940,7 +17946,7 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
@@ -17951,10 +17957,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17977,13 +17983,13 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18034,7 +18040,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -18055,7 +18061,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -18066,10 +18072,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18092,13 +18098,13 @@
         <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18149,7 +18155,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18170,7 +18176,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -18181,10 +18187,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18207,19 +18213,19 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
@@ -18268,7 +18274,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18286,10 +18292,10 @@
         <v>81</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -18300,10 +18306,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18326,13 +18332,13 @@
         <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18383,7 +18389,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18404,7 +18410,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -18415,14 +18421,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18444,13 +18450,13 @@
         <v>135</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18491,7 +18497,7 @@
         <v>138</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>81</v>
@@ -18500,7 +18506,7 @@
         <v>139</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18521,7 +18527,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18532,10 +18538,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18558,16 +18564,16 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18617,7 +18623,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18626,7 +18632,7 @@
         <v>90</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>102</v>
@@ -18638,21 +18644,21 @@
         <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18675,23 +18681,23 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q133" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="R133" t="s" s="2">
         <v>81</v>
@@ -18736,7 +18742,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18745,7 +18751,7 @@
         <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>102</v>
@@ -18757,21 +18763,21 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18794,16 +18800,16 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18853,7 +18859,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18871,24 +18877,24 @@
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18911,13 +18917,13 @@
         <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18968,7 +18974,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18986,24 +18992,24 @@
         <v>81</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19026,16 +19032,16 @@
         <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19085,7 +19091,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19103,10 +19109,10 @@
         <v>81</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19117,10 +19123,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19143,13 +19149,13 @@
         <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19200,7 +19206,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19221,7 +19227,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -19232,14 +19238,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19261,13 +19267,13 @@
         <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19308,7 +19314,7 @@
         <v>138</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>81</v>
@@ -19317,7 +19323,7 @@
         <v>139</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19338,7 +19344,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19349,10 +19355,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19375,19 +19381,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -19436,7 +19442,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19457,21 +19463,21 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19497,20 +19503,20 @@
         <v>110</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q140" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="R140" t="s" s="2">
         <v>81</v>
@@ -19531,13 +19537,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19555,7 +19561,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19576,21 +19582,21 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19613,17 +19619,17 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19672,7 +19678,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19693,21 +19699,21 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19733,14 +19739,14 @@
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19789,7 +19795,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19798,7 +19804,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -19810,21 +19816,21 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19850,16 +19856,16 @@
         <v>110</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19908,7 +19914,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19929,21 +19935,21 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19966,13 +19972,13 @@
         <v>81</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20023,7 +20029,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20044,10 +20050,10 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -20055,10 +20061,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20081,13 +20087,13 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20138,7 +20144,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20156,10 +20162,10 @@
         <v>81</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>81</v>
@@ -20170,10 +20176,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20196,13 +20202,13 @@
         <v>81</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20253,7 +20259,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20274,7 +20280,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20285,14 +20291,14 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20314,13 +20320,13 @@
         <v>135</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20370,7 +20376,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20391,7 +20397,7 @@
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
@@ -20402,14 +20408,14 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -20431,16 +20437,16 @@
         <v>135</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20489,7 +20495,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20521,10 +20527,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20547,16 +20553,16 @@
         <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20582,13 +20588,13 @@
         <v>81</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20606,7 +20612,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>90</v>
@@ -20624,24 +20630,24 @@
         <v>81</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20664,13 +20670,13 @@
         <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20697,13 +20703,13 @@
         <v>81</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>81</v>
@@ -20721,7 +20727,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20739,24 +20745,24 @@
         <v>81</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20779,13 +20785,13 @@
         <v>81</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20836,7 +20842,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20851,13 +20857,13 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>81</v>
@@ -20868,14 +20874,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20894,16 +20900,16 @@
         <v>81</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20953,7 +20959,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20974,7 +20980,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -20985,10 +20991,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21011,16 +21017,16 @@
         <v>81</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21070,7 +21076,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21085,13 +21091,13 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:49:26+00:00</t>
+    <t>2026-05-12T12:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T12:57:02+00:00</t>
+    <t>2026-05-12T16:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-inpatient-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:45:43+00:00</t>
+    <t>2026-05-18T17:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
